--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487984_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487984_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3101</v>
+        <v>1.208</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5009</v>
+        <v>1.208</v>
       </c>
       <c r="F2" t="n">
-        <v>1.811</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.0167</v>
+        <v>1.208</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5655</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.5822</v>
+        <v>0.6027</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4499</v>
+        <v>1.208</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7477</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.1975</v>
+        <v>0.6027</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5668</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1822</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3847</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9733</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6637999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2593</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5956</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.208</v>
+        <v>0.5638</v>
       </c>
       <c r="E3" t="n">
-        <v>1.208</v>
+        <v>-1.191</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.7548</v>
       </c>
       <c r="G3" t="n">
-        <v>1.208</v>
+        <v>-1.0167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.5655</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6027</v>
+        <v>-1.5822</v>
       </c>
       <c r="J3" t="n">
-        <v>1.208</v>
+        <v>-0.4499</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.7477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6027</v>
+        <v>-1.1975</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.5668</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.1822</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.3847</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.9733</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.5692</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.174</v>
+        <v>0.1152</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3378</v>
+        <v>0.0951</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1639</v>
+        <v>0.0201</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5803</v>
+        <v>-0.5836</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7574</v>
+        <v>-1.1727</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.1771</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5454</v>
+        <v>-0.3294</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8205</v>
+        <v>-0.3696</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.2751</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>0.035</v>
+        <v>-0.2542</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0631</v>
+        <v>-0.8032</v>
       </c>
       <c r="O4" t="n">
-        <v>1.098</v>
+        <v>0.549</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9822</v>
+        <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9493</v>
+        <v>-0.1625</v>
       </c>
       <c r="T4" t="n">
-        <v>1.854</v>
+        <v>0.1579</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.3203</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.3468</v>
+        <v>0.2666</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0704</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>J. LUQUE GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0248</v>
+        <v>0.0989</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0327</v>
+        <v>-0.8925</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5836</v>
+        <v>0.8014</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1727</v>
+        <v>-1.504</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5891999999999999</v>
+        <v>2.3054</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3294</v>
+        <v>1.1547</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3696</v>
+        <v>-0.5846</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>1.7393</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2542</v>
+        <v>-0.3533</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8032</v>
+        <v>-0.9194</v>
       </c>
       <c r="O5" t="n">
-        <v>0.549</v>
+        <v>0.5661</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5947</v>
+        <v>2.5769</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2529</v>
+        <v>-1.1664</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0955</v>
+        <v>0.1332</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3484</v>
+        <v>-1.2997</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2666</v>
+        <v>0.0674</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LUQUE GOMEZ</t>
+          <t>E. LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.261</v>
+        <v>-0.2426</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9154</v>
+        <v>-0.9816</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6544</v>
+        <v>0.739</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8014</v>
+        <v>-1.0448</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.504</v>
+        <v>-1.3164</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3054</v>
+        <v>0.2717</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1547</v>
+        <v>-1.0487</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5846</v>
+        <v>-1.0487</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7393</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3533</v>
+        <v>0.0039</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9194</v>
+        <v>-0.2677</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5661</v>
+        <v>0.2717</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5769</v>
+        <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5263</v>
+        <v>0.2074</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1103</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.6366</v>
+        <v>0.1404</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. LOPEZ GARCIA</t>
+          <t>F. MONTIEL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6325</v>
+        <v>-0.6531</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2872</v>
+        <v>-2.492</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6548</v>
+        <v>1.8389</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0448</v>
+        <v>-0.5099</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3164</v>
+        <v>-1.2751</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2717</v>
+        <v>0.7652</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0487</v>
+        <v>-1.1367</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0487</v>
+        <v>-1.217</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0039</v>
+        <v>0.6267</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2677</v>
+        <v>-0.0581</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2717</v>
+        <v>0.6848</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1824</v>
+        <v>0.2533</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2386</v>
+        <v>0.6269</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0562</v>
+        <v>-0.3736</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. MONTIEL RODRIGUEZ</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1967</v>
+        <v>-0.7304</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0637</v>
+        <v>0.5458</v>
       </c>
       <c r="F8" t="n">
-        <v>1.867</v>
+        <v>-1.2762</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5099</v>
+        <v>0.5803</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2751</v>
+        <v>2.7574</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7652</v>
+        <v>-2.1771</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1367</v>
+        <v>0.5454</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.217</v>
+        <v>3.8205</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0804</v>
+        <v>-3.2751</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6267</v>
+        <v>0.035</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0581</v>
+        <v>-1.0631</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6848</v>
+        <v>1.098</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2904</v>
+        <v>0.045</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0552</v>
+        <v>1.062</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3455</v>
+        <v>-1.017</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.3468</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.2764</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4657</v>
+        <v>-1.0863</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0132</v>
+        <v>-0.1444</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4526</v>
+        <v>-0.9419</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2461</v>
+        <v>1.2157</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1614</v>
+        <v>1.3878</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4075</v>
+        <v>-0.1721</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0404</v>
+        <v>2.2424</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0404</v>
+        <v>2.3072</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.0648</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2057</v>
+        <v>-1.0267</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2018</v>
+        <v>-0.9194</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4075</v>
+        <v>-0.1073</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1982</v>
+        <v>2.7751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3153</v>
+        <v>-1.4904</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0624</v>
+        <v>-0.2063</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2529</v>
+        <v>-1.2841</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6036</v>
+        <v>-1.4063</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6036</v>
+        <v>-1.4063</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.609</v>
+        <v>-1.4376</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8486</v>
+        <v>-1.0132</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7604</v>
+        <v>-0.4245</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5467</v>
+        <v>0.2461</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8145</v>
+        <v>-0.1614</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2678</v>
+        <v>0.4075</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4912</v>
+        <v>0.0404</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6117</v>
+        <v>0.0404</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1205</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0556</v>
+        <v>0.2057</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2028</v>
+        <v>-0.2018</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1472</v>
+        <v>0.4075</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1893</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.982</v>
+        <v>-0.2873</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4257</v>
+        <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5562</v>
+        <v>-0.2249</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2696</v>
+        <v>-0.6036</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5362</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6924</v>
+        <v>-1.5851</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7786</v>
+        <v>-0.6843</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.9008</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2157</v>
+        <v>-1.5467</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3878</v>
+        <v>-1.8145</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1721</v>
+        <v>0.2678</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2424</v>
+        <v>-0.4912</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3072</v>
+        <v>-0.6117</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0648</v>
+        <v>0.1205</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0267</v>
+        <v>-1.0556</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9194</v>
+        <v>-1.2028</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1073</v>
+        <v>0.1472</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5947</v>
+        <v>1.1893</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7751</v>
+        <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0964</v>
+        <v>-0.9581</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8405</v>
+        <v>-0.2615</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.256</v>
+        <v>-0.6966</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4063</v>
+        <v>-0.2696</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4063</v>
+        <v>-0.5362</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CORTES ANDRADES</t>
+          <t>D. GUAITA MACHADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.252</v>
+        <v>-1.7125</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.404</v>
+        <v>-1.8733</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.848</v>
+        <v>0.1608</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8244</v>
+        <v>0.1467</v>
       </c>
       <c r="H12" t="n">
-        <v>0.371</v>
+        <v>-0.8101</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4534</v>
+        <v>0.9568</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2758</v>
+        <v>1.2393</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3159</v>
+        <v>0.1752</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0402</v>
+        <v>1.0641</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1002</v>
+        <v>-1.0927</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6870000000000001</v>
+        <v>-0.9853</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4132</v>
+        <v>-0.1073</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9822</v>
+        <v>-3.1716</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7929</v>
+        <v>3.3698</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2606</v>
+        <v>-0.9177</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5874</v>
+        <v>0.0589</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3268</v>
+        <v>-0.9766</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1476</v>
+        <v>-1.1397</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4142</v>
+        <v>-1.1397</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. GUAITA MACHADO</t>
+          <t>D. CORTES ANDRADES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6023</v>
+        <v>-2.597</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8755</v>
+        <v>-1.7491</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2731</v>
+        <v>-0.848</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1467</v>
+        <v>0.8244</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8101</v>
+        <v>0.371</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9568</v>
+        <v>0.4534</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2393</v>
+        <v>-0.2758</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1752</v>
+        <v>-0.3159</v>
       </c>
       <c r="L13" t="n">
-        <v>1.0641</v>
+        <v>0.0402</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0927</v>
+        <v>1.1002</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9853</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1073</v>
+        <v>0.4132</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1716</v>
+        <v>-1.9822</v>
       </c>
       <c r="R13" t="n">
-        <v>3.3698</v>
+        <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8075</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9432</v>
+        <v>0.2423</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8643</v>
+        <v>-0.3268</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1397</v>
+        <v>-2.1476</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1397</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.9947</v>
+        <v>-8.0587</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.1086</v>
+        <v>-9.172500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1137</v>
+        <v>1.1136</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3209000000000001</v>
+        <v>0.3209000000000002</v>
       </c>
       <c r="H14" t="n">
         <v>-2.3672</v>
@@ -1546,13 +1546,13 @@
         <v>18.8312</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.5795</v>
+        <v>-4.643800000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4513</v>
+        <v>2.387300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.030800000000001</v>
+        <v>-7.030900000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-6.7095</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.6755</v>
+        <v>8.989000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7233</v>
+        <v>5.2327</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9522</v>
+        <v>3.7563</v>
       </c>
       <c r="G15" t="n">
         <v>4.1839</v>
@@ -1624,13 +1624,13 @@
         <v>2.5769</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2053</v>
+        <v>1.5187</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0476</v>
+        <v>0.4618</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2528</v>
+        <v>1.057</v>
       </c>
       <c r="V15" t="n">
         <v>3.0882</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7691</v>
+        <v>4.4844</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2523</v>
+        <v>1.928</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5167</v>
+        <v>2.5563</v>
       </c>
       <c r="G16" t="n">
         <v>0.5442</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4053</v>
+        <v>1.1206</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0412</v>
+        <v>0.7169</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6359</v>
+        <v>0.4037</v>
       </c>
       <c r="V16" t="n">
         <v>3.0178</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0828</v>
+        <v>4.0042</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4525</v>
+        <v>1.5543</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6304</v>
+        <v>2.4499</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0409</v>
@@ -1780,13 +1780,13 @@
         <v>2.9733</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0554</v>
+        <v>1.9768</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4355</v>
+        <v>1.5374</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3801</v>
+        <v>0.4395</v>
       </c>
       <c r="V17" t="n">
         <v>1.4737</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3538</v>
+        <v>2.8896</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2959</v>
+        <v>0.5191</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6496</v>
+        <v>2.3705</v>
       </c>
       <c r="G18" t="n">
         <v>2.0373</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1394</v>
+        <v>0.3964</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6864</v>
+        <v>0.1286</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4531</v>
+        <v>0.2679</v>
       </c>
       <c r="V18" t="n">
         <v>-0.337</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. RAGA RODRÍGUEZ</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3027</v>
+        <v>1.6635</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3027</v>
+        <v>0.2412</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.4223</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3027</v>
+        <v>0.1125</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3027</v>
+        <v>0.5526</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.4401</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3027</v>
+        <v>0.7531</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3027</v>
+        <v>0.6728</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.1201</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.5205</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.7581</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.4792</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2789</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>R. RAGA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0344</v>
+        <v>0.3027</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7775</v>
+        <v>0.3027</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7431</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1125</v>
+        <v>0.3027</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5526</v>
+        <v>0.3027</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4401</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7531</v>
+        <v>0.3027</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6728</v>
+        <v>0.3027</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6405999999999999</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1201</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5205</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9398</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5395</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4002</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.146</v>
+        <v>0.1425</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5231</v>
+        <v>-2.108</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3771</v>
+        <v>2.2505</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4909</v>
+        <v>-0.786</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7682</v>
+        <v>-0.786</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2774</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1009</v>
+        <v>-1.217</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1009</v>
+        <v>0.1412</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.3583</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5918</v>
+        <v>0.431</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8691</v>
+        <v>-0.9272</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2774</v>
+        <v>1.3583</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0079</v>
+        <v>0.2634</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3671</v>
+        <v>0.1001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6408</v>
+        <v>0.1632</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2666</v>
+        <v>0.0704</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2666</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. ALVAREZ ALVAREZ</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2018</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2018</v>
+        <v>0.1198</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2018</v>
+        <v>-0.4909</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2018</v>
+        <v>-0.7682</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.2774</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.1009</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.1009</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2018</v>
+        <v>-0.5918</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2018</v>
+        <v>-0.8691</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.2774</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.0563</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.6728</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.3835</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>N. ALVAREZ ALVAREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3059</v>
+        <v>-0.0999</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8211</v>
+        <v>0.1019</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5152</v>
+        <v>-0.2018</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.786</v>
+        <v>-0.2018</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.786</v>
+        <v>-0.2018</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.217</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1412</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3583</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.431</v>
+        <v>-0.2018</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9272</v>
+        <v>-0.2018</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3583</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.185</v>
+        <v>0.1019</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6129</v>
+        <v>0.1019</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5721000000000001</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3168</v>
+        <v>-1.1307</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7698</v>
+        <v>-1.6679</v>
       </c>
       <c r="F24" t="n">
-        <v>0.453</v>
+        <v>0.5372</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5800999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1421</v>
+        <v>0.044</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0046</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8019</v>
+        <v>-3.2647</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2795</v>
+        <v>-2.2151</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5224</v>
+        <v>-1.0496</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5384</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1835</v>
+        <v>1.7208</v>
       </c>
       <c r="T25" t="n">
-        <v>3.7114</v>
+        <v>1.7759</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5279</v>
+        <v>-0.0552</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4737</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3823</v>
+        <v>-4.1341</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.3776</v>
+        <v>-4.785</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0047</v>
+        <v>0.6509</v>
       </c>
       <c r="G26" t="n">
         <v>-4.8633</v>
@@ -2482,13 +2482,13 @@
         <v>1.5858</v>
       </c>
       <c r="S26" t="n">
-        <v>1.1284</v>
+        <v>1.3765</v>
       </c>
       <c r="T26" t="n">
-        <v>1.4244</v>
+        <v>1.017</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2961</v>
+        <v>0.3596</v>
       </c>
       <c r="V26" t="n">
         <v>1.1367</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>8.994799999999998</v>
+        <v>13.7489</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.1137</v>
+        <v>-1.1136</v>
       </c>
       <c r="F27" t="n">
-        <v>10.1084</v>
+        <v>14.8623</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3207999999999984</v>
+        <v>-0.3207999999999993</v>
       </c>
       <c r="H27" t="n">
         <v>2.367099999999998</v>
@@ -2560,13 +2560,13 @@
         <v>15.8579</v>
       </c>
       <c r="S27" t="n">
-        <v>5.579499999999999</v>
+        <v>10.3335</v>
       </c>
       <c r="T27" t="n">
-        <v>7.030799999999999</v>
+        <v>7.0311</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.4515</v>
+        <v>3.302699999999999</v>
       </c>
       <c r="V27" t="n">
         <v>6.7095</v>
